--- a/Data/dim_product.xlsx
+++ b/Data/dim_product.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\2\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\2- Sysco\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05323AA-9395-4C42-9B07-FB36C3F17070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3983CE5-04D4-48D7-995B-1779FE152E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
@@ -41,36 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="162">
   <si>
-    <t>Product Key</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Supplier Key</t>
-  </si>
-  <si>
-    <t>Category Key</t>
-  </si>
-  <si>
-    <t>Quantity Per Unit</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Units in Stock</t>
-  </si>
-  <si>
-    <t>Units on Order</t>
-  </si>
-  <si>
-    <t>Reorder Level</t>
-  </si>
-  <si>
-    <t>Discontinued</t>
-  </si>
-  <si>
     <t>Need Reorder</t>
   </si>
   <si>
@@ -525,6 +495,36 @@
   </si>
   <si>
     <t>12 boxes</t>
+  </si>
+  <si>
+    <t>product_key</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>supplier_key</t>
+  </si>
+  <si>
+    <t>category_key</t>
+  </si>
+  <si>
+    <t>quantity_per_unit</t>
+  </si>
+  <si>
+    <t>unit_price</t>
+  </si>
+  <si>
+    <t>units_in_stock</t>
+  </si>
+  <si>
+    <t>units_on_order</t>
+  </si>
+  <si>
+    <t>reorder_level</t>
+  </si>
+  <si>
+    <t>discontinued</t>
   </si>
 </sst>
 </file>
@@ -909,40 +909,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -950,7 +950,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -959,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1">
         <v>18</v>
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -988,7 +988,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -997,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1">
         <v>19</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1026,7 +1026,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -1035,7 +1035,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1">
         <v>10</v>
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1064,7 +1064,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
@@ -1073,7 +1073,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1">
         <v>22</v>
@@ -1091,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1102,7 +1102,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
@@ -1111,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1">
         <v>21.35</v>
@@ -1129,10 +1129,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1140,7 +1140,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -1149,7 +1149,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1">
         <v>25</v>
@@ -1167,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1178,7 +1178,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -1187,7 +1187,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F8" s="1">
         <v>30</v>
@@ -1205,10 +1205,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2">
         <v>3</v>
@@ -1225,7 +1225,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
         <v>40</v>
@@ -1243,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1254,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
@@ -1263,7 +1263,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1">
         <v>97</v>
@@ -1281,10 +1281,10 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1292,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
@@ -1301,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1">
         <v>31</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1330,7 +1330,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2">
         <v>5</v>
@@ -1339,7 +1339,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1">
         <v>21</v>
@@ -1357,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1368,7 +1368,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>
@@ -1377,7 +1377,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1">
         <v>38</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1406,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2">
         <v>6</v>
@@ -1415,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F14" s="1">
         <v>6</v>
@@ -1433,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1444,7 +1444,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2">
         <v>6</v>
@@ -1453,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F15" s="1">
         <v>23.25</v>
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1482,7 +1482,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2">
         <v>6</v>
@@ -1491,7 +1491,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1">
         <v>15.5</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1520,7 +1520,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
@@ -1529,7 +1529,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F17" s="1">
         <v>17.45</v>
@@ -1547,10 +1547,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1558,7 +1558,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2">
         <v>7</v>
@@ -1567,7 +1567,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F18" s="1">
         <v>39</v>
@@ -1585,10 +1585,10 @@
         <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1596,7 +1596,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -1605,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F19" s="1">
         <v>62.5</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1634,7 +1634,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F20" s="1">
         <v>9.1999999999999993</v>
@@ -1661,10 +1661,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1672,7 +1672,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2">
         <v>8</v>
@@ -1681,7 +1681,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F21" s="1">
         <v>81</v>
@@ -1699,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2">
         <v>8</v>
@@ -1719,7 +1719,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F22" s="1">
         <v>10</v>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1748,7 +1748,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2">
         <v>9</v>
@@ -1757,7 +1757,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1">
         <v>21</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1786,7 +1786,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2">
         <v>9</v>
@@ -1795,7 +1795,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F24" s="1">
         <v>9</v>
@@ -1813,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1824,7 +1824,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2">
         <v>10</v>
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F25" s="1">
         <v>4.5</v>
@@ -1851,10 +1851,10 @@
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1862,7 +1862,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2">
         <v>11</v>
@@ -1871,7 +1871,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F26" s="1">
         <v>14</v>
@@ -1889,10 +1889,10 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1900,7 +1900,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2">
         <v>11</v>
@@ -1909,7 +1909,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F27" s="1">
         <v>31.23</v>
@@ -1927,10 +1927,10 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C28" s="2">
         <v>11</v>
@@ -1947,7 +1947,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F28" s="1">
         <v>43.9</v>
@@ -1965,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1976,7 +1976,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2">
         <v>12</v>
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F29" s="1">
         <v>45.6</v>
@@ -2003,10 +2003,10 @@
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2014,7 +2014,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F30" s="1">
         <v>123.79</v>
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2052,7 +2052,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C31" s="2">
         <v>13</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F31" s="1">
         <v>25.89</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2090,7 +2090,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2">
         <v>14</v>
@@ -2099,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F32" s="1">
         <v>12.5</v>
@@ -2117,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2128,7 +2128,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C33" s="2">
         <v>14</v>
@@ -2137,7 +2137,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F33" s="1">
         <v>32</v>
@@ -2155,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2166,7 +2166,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2">
         <v>15</v>
@@ -2175,7 +2175,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F34" s="1">
         <v>2.5</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2204,7 +2204,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>16</v>
@@ -2213,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F35" s="1">
         <v>14</v>
@@ -2231,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2242,7 +2242,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>16</v>
@@ -2251,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F36" s="1">
         <v>18</v>
@@ -2269,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2280,7 +2280,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C37" s="2">
         <v>17</v>
@@ -2289,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F37" s="1">
         <v>19</v>
@@ -2307,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2318,7 +2318,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C38" s="2">
         <v>17</v>
@@ -2327,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F38" s="1">
         <v>26</v>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2356,7 +2356,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C39" s="2">
         <v>18</v>
@@ -2365,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F39" s="1">
         <v>263.5</v>
@@ -2383,10 +2383,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2394,7 +2394,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2">
         <v>18</v>
@@ -2403,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F40" s="1">
         <v>18</v>
@@ -2421,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C41" s="2">
         <v>19</v>
@@ -2441,7 +2441,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F41" s="1">
         <v>18.399999999999999</v>
@@ -2459,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2470,7 +2470,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C42" s="2">
         <v>19</v>
@@ -2479,7 +2479,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F42" s="1">
         <v>9.65</v>
@@ -2497,10 +2497,10 @@
         <v>0</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2508,7 +2508,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C43" s="2">
         <v>20</v>
@@ -2517,7 +2517,7 @@
         <v>5</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F43" s="1">
         <v>14</v>
@@ -2535,10 +2535,10 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2546,7 +2546,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C44" s="2">
         <v>20</v>
@@ -2555,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F44" s="1">
         <v>46</v>
@@ -2573,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2584,7 +2584,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C45" s="2">
         <v>20</v>
@@ -2593,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F45" s="1">
         <v>19.45</v>
@@ -2611,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2622,7 +2622,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C46" s="2">
         <v>21</v>
@@ -2631,7 +2631,7 @@
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F46" s="1">
         <v>9.5</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2660,7 +2660,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C47" s="2">
         <v>21</v>
@@ -2669,7 +2669,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F47" s="1">
         <v>12</v>
@@ -2687,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2698,7 +2698,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C48" s="2">
         <v>22</v>
@@ -2707,7 +2707,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F48" s="1">
         <v>9.5</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2736,7 +2736,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C49" s="2">
         <v>22</v>
@@ -2745,7 +2745,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F49" s="1">
         <v>12.75</v>
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2774,7 +2774,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2">
         <v>23</v>
@@ -2783,7 +2783,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1">
         <v>20</v>
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2812,7 +2812,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C51" s="2">
         <v>23</v>
@@ -2821,7 +2821,7 @@
         <v>3</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F51" s="1">
         <v>16.25</v>
@@ -2839,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2850,7 +2850,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2">
         <v>24</v>
@@ -2859,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="F52" s="1">
         <v>53</v>
@@ -2877,10 +2877,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2888,7 +2888,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C53" s="2">
         <v>24</v>
@@ -2897,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F53" s="1">
         <v>7</v>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2926,7 +2926,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C54" s="2">
         <v>24</v>
@@ -2935,7 +2935,7 @@
         <v>6</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F54" s="1">
         <v>32.799999999999997</v>
@@ -2953,10 +2953,10 @@
         <v>1</v>
       </c>
       <c r="K54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2964,7 +2964,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C55" s="2">
         <v>25</v>
@@ -2973,7 +2973,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F55" s="1">
         <v>7.45</v>
@@ -2991,10 +2991,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C56" s="2">
         <v>25</v>
@@ -3011,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F56" s="1">
         <v>24</v>
@@ -3029,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,7 +3040,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C57" s="2">
         <v>26</v>
@@ -3049,7 +3049,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F57" s="1">
         <v>38</v>
@@ -3067,10 +3067,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3078,7 +3078,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C58" s="2">
         <v>26</v>
@@ -3087,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F58" s="1">
         <v>19.5</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3116,7 +3116,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C59" s="2">
         <v>27</v>
@@ -3125,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F59" s="1">
         <v>13.25</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3154,7 +3154,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C60" s="2">
         <v>28</v>
@@ -3163,7 +3163,7 @@
         <v>4</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F60" s="1">
         <v>55</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3192,7 +3192,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C61" s="2">
         <v>28</v>
@@ -3201,7 +3201,7 @@
         <v>4</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F61" s="1">
         <v>34</v>
@@ -3219,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3230,7 +3230,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C62" s="2">
         <v>29</v>
@@ -3239,7 +3239,7 @@
         <v>2</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F62" s="1">
         <v>28.5</v>
@@ -3257,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3268,7 +3268,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2">
         <v>29</v>
@@ -3277,7 +3277,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F63" s="1">
         <v>49.3</v>
@@ -3295,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3306,7 +3306,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2">
         <v>7</v>
@@ -3315,7 +3315,7 @@
         <v>2</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F64" s="1">
         <v>43.9</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3344,7 +3344,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2">
         <v>12</v>
@@ -3353,7 +3353,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F65" s="1">
         <v>33.25</v>
@@ -3371,10 +3371,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3382,7 +3382,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C66" s="2">
         <v>2</v>
@@ -3391,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F66" s="1">
         <v>21.05</v>
@@ -3409,10 +3409,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3420,7 +3420,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C67" s="2">
         <v>2</v>
@@ -3429,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F67" s="1">
         <v>17</v>
@@ -3447,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3458,7 +3458,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C68" s="2">
         <v>16</v>
@@ -3467,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F68" s="1">
         <v>14</v>
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3496,7 +3496,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F69" s="1">
         <v>12.5</v>
@@ -3523,10 +3523,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C70" s="2">
         <v>15</v>
@@ -3543,7 +3543,7 @@
         <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F70" s="1">
         <v>36</v>
@@ -3561,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3572,7 +3572,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C71" s="2">
         <v>7</v>
@@ -3581,7 +3581,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F71" s="1">
         <v>15</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3610,7 +3610,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C72" s="2">
         <v>15</v>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1">
         <v>21.5</v>
@@ -3637,10 +3637,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3648,7 +3648,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C73" s="2">
         <v>14</v>
@@ -3657,7 +3657,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F73" s="1">
         <v>34.799999999999997</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3686,7 +3686,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C74" s="2">
         <v>17</v>
@@ -3695,7 +3695,7 @@
         <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F74" s="1">
         <v>15</v>
@@ -3713,10 +3713,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3724,7 +3724,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C75" s="2">
         <v>4</v>
@@ -3733,7 +3733,7 @@
         <v>7</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F75" s="1">
         <v>10</v>
@@ -3751,10 +3751,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3762,7 +3762,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C76" s="2">
         <v>12</v>
@@ -3771,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F76" s="1">
         <v>7.75</v>
@@ -3789,10 +3789,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3800,7 +3800,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2">
         <v>23</v>
@@ -3809,7 +3809,7 @@
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F77" s="1">
         <v>18</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3838,7 +3838,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C78" s="2">
         <v>12</v>
@@ -3847,7 +3847,7 @@
         <v>2</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F78" s="1">
         <v>13</v>
@@ -3865,10 +3865,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
